--- a/frontend/public/template/Portfolio_AI_Template_USA.xlsx
+++ b/frontend/public/template/Portfolio_AI_Template_USA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\AI\git\portfolio_ai\frontend\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150B332E-E150-44F6-811B-DF766860F7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF4D047-C59A-4215-AB39-F7E58A98D6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Investor" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>Name</t>
   </si>
@@ -90,9 +90,6 @@
     <t>NYSE</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Vanguard S&amp;P 500 ETF</t>
   </si>
   <si>
@@ -123,19 +120,10 @@
     <t>BND</t>
   </si>
   <si>
-    <t>Bond ETF</t>
-  </si>
-  <si>
     <t>iShares Treasury ETF</t>
   </si>
   <si>
     <t>SHY</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>ETF</t>
   </si>
   <si>
     <t>Ticker</t>
@@ -203,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -215,6 +203,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -554,152 +548,149 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.109375" customWidth="1"/>
-    <col min="2" max="2" width="26.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="8">
         <v>10</v>
       </c>
-      <c r="D2" s="4">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="D2" s="8">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="8">
         <v>5</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="8">
         <v>420</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="8">
         <v>20</v>
       </c>
-      <c r="D4" s="4">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="D4" s="8">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="8">
         <v>10</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="8">
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="8">
         <v>5</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="8">
         <v>250</v>
       </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="8">
         <v>20</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="8">
         <v>190</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="8">
         <v>12</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="8">
         <v>62</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.109375" customWidth="1"/>
+    <col min="1" max="1" width="34.33203125" customWidth="1"/>
     <col min="2" max="2" width="15.77734375" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>9</v>
@@ -707,16 +698,13 @@
       <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="C2" s="3">
         <v>20</v>
@@ -724,16 +712,13 @@
       <c r="D2" s="3">
         <v>450</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="C3" s="3">
         <v>15</v>
@@ -741,16 +726,13 @@
       <c r="D3" s="3">
         <v>270</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="C4" s="3">
         <v>10</v>
@@ -758,16 +740,13 @@
       <c r="D4" s="3">
         <v>460</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="3">
         <v>12</v>
@@ -775,16 +754,13 @@
       <c r="D5" s="3">
         <v>550</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C6" s="2">
         <v>50</v>
@@ -792,25 +768,19 @@
       <c r="D6" s="2">
         <v>72</v>
       </c>
-      <c r="E6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="C7" s="2">
         <v>30</v>
       </c>
       <c r="D7" s="2">
         <v>82</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
